--- a/output/roomself_excel/10611.xlsx
+++ b/output/roomself_excel/10611.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>125972</v>
+        <v>90387</v>
       </c>
       <c r="D2" t="n">
-        <v>2868</v>
+        <v>2448</v>
       </c>
       <c r="E2" t="n">
-        <v>425</v>
+        <v>249</v>
       </c>
       <c r="F2" t="n">
-        <v>324</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>95143</v>
+        <v>157648</v>
       </c>
       <c r="D3" t="n">
-        <v>3600</v>
+        <v>3180</v>
       </c>
       <c r="E3" t="n">
-        <v>667</v>
+        <v>425</v>
       </c>
       <c r="F3" t="n">
-        <v>474</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>40508</v>
+        <v>72161</v>
       </c>
       <c r="D4" t="n">
-        <v>1644</v>
+        <v>2156</v>
       </c>
       <c r="E4" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F4" t="n">
-        <v>180</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>393537</v>
+        <v>125972</v>
       </c>
       <c r="D5" t="n">
-        <v>8640</v>
+        <v>2868</v>
       </c>
       <c r="E5" t="n">
-        <v>902</v>
+        <v>425</v>
       </c>
       <c r="F5" t="n">
-        <v>665</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>78052</v>
+        <v>127199</v>
       </c>
       <c r="D6" t="n">
-        <v>2252</v>
+        <v>2880</v>
       </c>
       <c r="E6" t="n">
-        <v>316</v>
+        <v>425</v>
       </c>
       <c r="F6" t="n">
-        <v>16</v>
+        <v>327</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>127199</v>
+        <v>78052</v>
       </c>
       <c r="D7" t="n">
-        <v>2880</v>
+        <v>2252</v>
       </c>
       <c r="E7" t="n">
-        <v>425</v>
+        <v>316</v>
       </c>
       <c r="F7" t="n">
-        <v>327</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>87084</v>
+        <v>28556</v>
       </c>
       <c r="D8" t="n">
-        <v>2420</v>
+        <v>1428</v>
       </c>
       <c r="E8" t="n">
-        <v>384</v>
+        <v>121</v>
       </c>
       <c r="F8" t="n">
-        <v>251</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24308</v>
+        <v>13077</v>
       </c>
       <c r="D9" t="n">
-        <v>1356</v>
+        <v>956</v>
       </c>
       <c r="E9" t="n">
-        <v>103</v>
+        <v>150</v>
       </c>
       <c r="F9" t="n">
-        <v>15</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>28556</v>
+        <v>77731</v>
       </c>
       <c r="D10" t="n">
-        <v>1428</v>
+        <v>2868</v>
       </c>
       <c r="E10" t="n">
-        <v>121</v>
+        <v>667</v>
       </c>
       <c r="F10" t="n">
-        <v>15</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13077</v>
+        <v>73341</v>
       </c>
       <c r="D11" t="n">
-        <v>956</v>
+        <v>3076</v>
       </c>
       <c r="E11" t="n">
-        <v>386</v>
+        <v>182</v>
       </c>
       <c r="F11" t="n">
-        <v>155</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30381</v>
+        <v>8200</v>
       </c>
       <c r="D12" t="n">
-        <v>1480</v>
+        <v>728</v>
       </c>
       <c r="E12" t="n">
-        <v>263</v>
+        <v>82</v>
       </c>
       <c r="F12" t="n">
-        <v>139</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -708,17 +708,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8200</v>
+        <v>17412</v>
       </c>
       <c r="D13" t="n">
-        <v>728</v>
+        <v>1108</v>
       </c>
       <c r="E13" t="n">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="F13" t="n">
         <v>16</v>
@@ -734,16 +734,104 @@
         </is>
       </c>
       <c r="C14" t="n">
+        <v>24308</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1356</v>
+      </c>
+      <c r="E14" t="n">
+        <v>103</v>
+      </c>
+      <c r="F14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
         <v>32248</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D15" t="n">
         <v>1576</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E15" t="n">
         <v>278</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F15" t="n">
         <v>148</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>40508</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1644</v>
+      </c>
+      <c r="E16" t="n">
+        <v>263</v>
+      </c>
+      <c r="F16" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>87084</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2420</v>
+      </c>
+      <c r="E17" t="n">
+        <v>384</v>
+      </c>
+      <c r="F17" t="n">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>30381</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1480</v>
+      </c>
+      <c r="E18" t="n">
+        <v>263</v>
+      </c>
+      <c r="F18" t="n">
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/10611.xlsx
+++ b/output/roomself_excel/10611.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,10 +495,26 @@
       <c r="D2" t="n">
         <v>2448</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>363</v>
+      </c>
+      <c r="G2" t="n">
+        <v>13</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>249</v>
       </c>
-      <c r="F2" t="n">
+      <c r="J2" t="n">
         <v>15</v>
       </c>
     </row>
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>3180</v>
       </c>
-      <c r="E3" t="n">
-        <v>425</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>399</v>
+        <v>410</v>
+      </c>
+      <c r="G3" t="n">
+        <v>15</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>384</v>
+      </c>
+      <c r="J3" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +571,27 @@
       <c r="D4" t="n">
         <v>2156</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>265</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>15</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>272</v>
+      </c>
+      <c r="J4" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -541,11 +609,27 @@
       <c r="D5" t="n">
         <v>2868</v>
       </c>
-      <c r="E5" t="n">
-        <v>425</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>324</v>
+        <v>409</v>
+      </c>
+      <c r="G5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>308</v>
+      </c>
+      <c r="J5" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -563,11 +647,27 @@
       <c r="D6" t="n">
         <v>2880</v>
       </c>
-      <c r="E6" t="n">
-        <v>425</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>327</v>
+        <v>311</v>
+      </c>
+      <c r="G6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>409</v>
+      </c>
+      <c r="J6" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -585,12 +685,20 @@
       <c r="D7" t="n">
         <v>2252</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>316</v>
       </c>
-      <c r="F7" t="n">
-        <v>16</v>
-      </c>
+      <c r="G7" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +715,20 @@
       <c r="D8" t="n">
         <v>1428</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>121</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>15</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,11 +745,27 @@
       <c r="D9" t="n">
         <v>956</v>
       </c>
-      <c r="E9" t="n">
-        <v>150</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>107</v>
+        <v>21</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>98</v>
+      </c>
+      <c r="J9" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -651,12 +783,20 @@
       <c r="D10" t="n">
         <v>2868</v>
       </c>
-      <c r="E10" t="n">
-        <v>667</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>87</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="G10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +813,20 @@
       <c r="D11" t="n">
         <v>3076</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>182</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>15</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +843,20 @@
       <c r="D12" t="n">
         <v>728</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>82</v>
       </c>
-      <c r="F12" t="n">
-        <v>16</v>
-      </c>
+      <c r="G12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +873,20 @@
       <c r="D13" t="n">
         <v>1108</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>113</v>
       </c>
-      <c r="F13" t="n">
-        <v>16</v>
-      </c>
+      <c r="G13" t="n">
+        <v>16</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +903,20 @@
       <c r="D14" t="n">
         <v>1356</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>103</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>15</v>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,11 +933,27 @@
       <c r="D15" t="n">
         <v>1576</v>
       </c>
-      <c r="E15" t="n">
-        <v>278</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>148</v>
+        <v>556</v>
+      </c>
+      <c r="G15" t="n">
+        <v>16</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>116</v>
+      </c>
+      <c r="J15" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -783,11 +971,27 @@
       <c r="D16" t="n">
         <v>1644</v>
       </c>
-      <c r="E16" t="n">
-        <v>263</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>180</v>
+        <v>247</v>
+      </c>
+      <c r="G16" t="n">
+        <v>16</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>164</v>
+      </c>
+      <c r="J16" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -805,11 +1009,27 @@
       <c r="D17" t="n">
         <v>2420</v>
       </c>
-      <c r="E17" t="n">
-        <v>384</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>251</v>
+        <v>236</v>
+      </c>
+      <c r="G17" t="n">
+        <v>15</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>369</v>
+      </c>
+      <c r="J17" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -827,11 +1047,27 @@
       <c r="D18" t="n">
         <v>1480</v>
       </c>
-      <c r="E18" t="n">
-        <v>263</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>139</v>
+        <v>123</v>
+      </c>
+      <c r="G18" t="n">
+        <v>16</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>115</v>
+      </c>
+      <c r="J18" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
